--- a/ch_08/ch_08_solution.xlsx
+++ b/ch_08/ch_08_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30515"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_08_simulations_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6763623-1E7A-4150-90D7-386467A0D74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70B9121-EE06-4569-8B91-6F6966910135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -112,7 +112,7 @@
   <pythonScripts>
     <pythonScript>
       <code># Set random seed for reproducibility
-# np.random.seed(42)
+np.random.seed(42)
 # Simulation parameters
 num_experiments = 10000
 flips_per_experiment = 100
@@ -809,114 +809,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.41015625" customWidth="1"/>
-    <col min="2" max="2" width="9.703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5859375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.17578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.3984375" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" cm="1">
         <f t="array" ref="A1:A5">_xlfn._xlws.PY(0,0)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="str" cm="1">
         <f t="array" ref="A8">_xlfn._xlws.PY(1,0)</f>
-        <v>Mean heads per 100 flips: 49.98, Std dev: 5.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.5">
+        <v>Mean heads per 100 flips: 49.98, Std dev: 4.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="e" cm="1" vm="1">
         <f t="array" ref="A11">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" cm="1">
         <f t="array" ref="A23:A27">_xlfn._xlws.PY(3,0)</f>
         <v>1099.3428306022465</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>972.34713976576302</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>1129.5377076201385</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>1304.605971281605</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>953.16932505533282</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" s="1" cm="1">
         <f t="array" ref="A30:A34">_xlfn._xlws.PY(4,0)</f>
         <v>21967.141530112327</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>15617.356988288149</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>22000</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>22000</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>14658.466252766644</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="str" cm="1">
         <f t="array" ref="A36:B41">_xlfn._xlws.PY(5,0)</f>
         <v>Metric</v>
@@ -925,7 +925,7 @@
         <v>Value</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
         <v>Mean Profit</v>
       </c>
@@ -933,7 +933,7 @@
         <v>14998.252053092408</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
         <v>Median Profit</v>
       </c>
@@ -941,7 +941,7 @@
         <v>16974.050242071222</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="str">
         <v>10th Percentile</v>
       </c>
@@ -949,7 +949,7 @@
         <v>4077.0103968971662</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <v>90th Percentile</v>
       </c>
@@ -957,7 +957,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <v>Probability of Loss</v>
       </c>
@@ -965,19 +965,19 @@
         <v>4.65E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="e" cm="1" vm="2">
         <f t="array" ref="A44">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" t="str" cm="1">
         <f t="array" ref="A58">_xlfn._xlws.PY(7,0)</f>
         <v>Probability of profit &gt; $18,000: 45.9%</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="str" cm="1">
         <f t="array" ref="A62:F65">_xlfn._xlws.PY(8,0)</f>
         <v>Inventory</v>
@@ -998,7 +998,7 @@
         <v>Prob of Loss</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="3">
         <v>900</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>1.06E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="3">
         <v>1100</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>4.65E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="3">
         <v>1300</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>0.13539999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" t="e" cm="1" vm="3">
         <f t="array" ref="A68">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
